--- a/logs/SpliceCLIP.xlsx
+++ b/logs/SpliceCLIP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikej\Documents\Career\Georges\Ule\projects\Spliceosome\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikej\Documents\Career\Georges\Ule\intron_retention_propensity\logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20B01D3-1CF2-4BE5-85FA-55A8D313B2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704F8A4A-F564-4C59-A74B-A3A5A7FC2A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-56220" yWindow="765" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
